--- a/uploads/final_output.xlsx
+++ b/uploads/final_output.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Institute-Exp Rec vs Non-Rec" sheetId="1" r:id="rId1"/>
-    <sheet name="T-Hub-Exp Rec vs Non-Rec" sheetId="2" r:id="rId2"/>
-    <sheet name="Overall Rec vs Non-Rec" sheetId="3" r:id="rId3"/>
+    <sheet name="TG-Wise Exp Rec vs Non-Rec" sheetId="2" r:id="rId2"/>
+    <sheet name="T-Hub-Exp Rec vs Non-Rec" sheetId="3" r:id="rId3"/>
+    <sheet name="Overall Rec vs Non-Rec" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="48">
   <si>
     <t>TG</t>
   </si>
@@ -115,6 +116,9 @@
   </si>
   <si>
     <t>RRI</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
   <si>
     <t>Hub</t>
@@ -177,7 +181,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Open Sans"/>
       <family val="2"/>
     </font>
@@ -203,7 +207,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A90E2"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1125,6 +1129,157 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="26" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3">
+        <v>137407455</v>
+      </c>
+      <c r="C2" s="3">
+        <v>20811809</v>
+      </c>
+      <c r="D2" s="3">
+        <v>116595646</v>
+      </c>
+      <c r="E2" s="3">
+        <v>239182832</v>
+      </c>
+      <c r="F2" s="3">
+        <v>12244733</v>
+      </c>
+      <c r="G2" s="3">
+        <v>226938099</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3">
+        <v>16996734</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7275621</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9721113</v>
+      </c>
+      <c r="E3" s="3">
+        <v>13925897</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2353634</v>
+      </c>
+      <c r="G3" s="3">
+        <v>11572263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>168922500</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5989467</v>
+      </c>
+      <c r="D4" s="3">
+        <v>162933033</v>
+      </c>
+      <c r="E4" s="3">
+        <v>120164750</v>
+      </c>
+      <c r="F4" s="3">
+        <v>33375241</v>
+      </c>
+      <c r="G4" s="3">
+        <v>86789509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>63747790</v>
+      </c>
+      <c r="C5" s="3">
+        <v>19700727</v>
+      </c>
+      <c r="D5" s="3">
+        <v>44047063</v>
+      </c>
+      <c r="E5" s="3">
+        <v>178585750</v>
+      </c>
+      <c r="F5" s="3">
+        <v>76521946</v>
+      </c>
+      <c r="G5" s="3">
+        <v>102063804</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3">
+        <v>387074479</v>
+      </c>
+      <c r="C6" s="3">
+        <v>53777624</v>
+      </c>
+      <c r="D6" s="3">
+        <v>333296855</v>
+      </c>
+      <c r="E6" s="3">
+        <v>551859229</v>
+      </c>
+      <c r="F6" s="3">
+        <v>124495554</v>
+      </c>
+      <c r="G6" s="3">
+        <v>427363675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1133,33 +1288,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3">
         <v>53000000</v>
@@ -1173,13 +1328,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3">
         <v>35835000</v>
@@ -1196,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1206,21 +1361,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3">
         <v>551859229</v>
@@ -1234,7 +1389,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
         <v>387074479</v>
